--- a/Result/profitability/5225.xlsx
+++ b/Result/profitability/5225.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>4.03</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8125</v>
+        <v>2.295</v>
       </c>
       <c r="N2" t="n">
-        <v>15.60875</v>
+        <v>14.66125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -8431,6 +8431,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2676</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E64" t="n">
+        <v>311</v>
+      </c>
+      <c r="F64" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="G64" t="n">
+        <v>16</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>26</v>
+      </c>
+      <c r="J64" t="n">
+        <v>42</v>
+      </c>
+      <c r="K64" t="n">
+        <v>30</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2.35625</v>
+      </c>
+      <c r="N64" t="n">
+        <v>15.5075</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="X64" t="n">
+        <v>-0.7532467532467533</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-0.218938885157824</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>-0.8741721854304636</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>-6.229999999999999</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>-0.3488241881298991</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
